--- a/artfynd/A 22456-2023 artfynd.xlsx
+++ b/artfynd/A 22456-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13439615</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13439616</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13439618</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13440212</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13440214</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13440219</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13440220</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13445574</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13445575</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13445576</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1948,6 +2003,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13445577</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2064,6 +2124,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13445578</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2180,6 +2245,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13445580</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2296,6 +2366,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13445581</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2412,6 +2487,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13445582</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2528,6 +2608,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13445586</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2649,6 +2734,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754640</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2770,6 +2860,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754641</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2891,6 +2986,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754642</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3012,6 +3112,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754643</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3133,6 +3238,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754644</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3254,6 +3364,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754645</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3375,6 +3490,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754646</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3496,6 +3616,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754647</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3617,6 +3742,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754648</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3738,6 +3868,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754649</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3859,6 +3994,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754650</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3980,6 +4120,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754651</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4101,6 +4246,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754652</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4222,6 +4372,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754653</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4343,6 +4498,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754654</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4464,6 +4624,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754655</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4585,6 +4750,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754656</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4706,6 +4876,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754657</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4827,6 +5002,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754658</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4948,6 +5128,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754659</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5069,6 +5254,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14262991</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5190,6 +5380,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14262992</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5311,6 +5506,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14262993</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5432,6 +5632,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14262994</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5553,6 +5758,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14262995</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5674,6 +5884,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14262996</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5795,6 +6010,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14263004</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5916,6 +6136,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14263006</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6037,6 +6262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14263007</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6158,6 +6388,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14263008</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6279,6 +6514,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14263009</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6400,6 +6640,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14263010</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6521,6 +6766,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14263011</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6642,6 +6892,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14263012</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6763,6 +7018,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619763</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6884,6 +7144,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619765</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7005,6 +7270,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619766</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7126,6 +7396,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619767</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7247,6 +7522,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619768</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7368,6 +7648,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619769</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7489,6 +7774,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619770</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7610,6 +7900,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619771</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7731,6 +8026,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619772</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7852,6 +8152,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619773</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7973,6 +8278,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619774</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8094,6 +8404,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14651134</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8215,6 +8530,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14651135</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8336,6 +8656,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14651136</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8457,6 +8782,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14651137</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8578,6 +8908,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14651138</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8699,6 +9034,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14651139</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8820,6 +9160,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14651140</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8941,6 +9286,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15196198</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9062,6 +9412,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15196199</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9183,6 +9538,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15196200</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9304,6 +9664,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15196201</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9425,6 +9790,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15196325</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9546,6 +9916,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15196326</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9677,6 +10052,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17290862</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9808,6 +10188,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17290863</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9934,6 +10319,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55768466</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10050,8 +10440,93 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4237289</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>